--- a/TEMPLATE RUN MEGER - Copy.xlsx
+++ b/TEMPLATE RUN MEGER - Copy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\python_mass_word_FINAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VNG\Downloads\Greennode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5829C2-DAE8-4DED-8E16-41F30791F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B81FCB9-D19E-473E-9A60-BBF4CDD7C09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F243D4EE-F9EC-4441-8F60-FB4044932F4E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="360">
   <si>
     <t>Bank</t>
   </si>
@@ -90,18 +90,6 @@
     <t>Connector Channel</t>
   </si>
   <si>
-    <t>SỐ DƯ</t>
-  </si>
-  <si>
-    <t>NGÀY TẠO VÍ</t>
-  </si>
-  <si>
-    <t>NGÀY LIÊN KẾT</t>
-  </si>
-  <si>
-    <t>LIÊN KẾT LẦN ĐẦU</t>
-  </si>
-  <si>
     <t>08/06/2026 17:24:17</t>
   </si>
   <si>
@@ -547,6 +535,591 @@
   </si>
   <si>
     <t>xxxxxxxxx</t>
+  </si>
+  <si>
+    <t>Bank 3</t>
+  </si>
+  <si>
+    <t>ZLPH16VO8C6MF</t>
+  </si>
+  <si>
+    <t>949201695725314</t>
+  </si>
+  <si>
+    <t>App ID 97</t>
+  </si>
+  <si>
+    <t>transtype1</t>
+  </si>
+  <si>
+    <t>Thanh toán mua C</t>
+  </si>
+  <si>
+    <t>Bank 2</t>
+  </si>
+  <si>
+    <t>ZLPZC6PW14DT6</t>
+  </si>
+  <si>
+    <t>047303825740150</t>
+  </si>
+  <si>
+    <t>App ID 39</t>
+  </si>
+  <si>
+    <t>transtype2</t>
+  </si>
+  <si>
+    <t>Thanh toán mua B</t>
+  </si>
+  <si>
+    <t>Bank 1</t>
+  </si>
+  <si>
+    <t>ZLP0L9E2YU689</t>
+  </si>
+  <si>
+    <t>064269509640082</t>
+  </si>
+  <si>
+    <t>App ID 4</t>
+  </si>
+  <si>
+    <t>transtype3</t>
+  </si>
+  <si>
+    <t>ZLPDSNQG3G8ZW</t>
+  </si>
+  <si>
+    <t>147387495416193</t>
+  </si>
+  <si>
+    <t>App ID 1</t>
+  </si>
+  <si>
+    <t>ZLPAKR34R9EDY</t>
+  </si>
+  <si>
+    <t>323326753065894</t>
+  </si>
+  <si>
+    <t>App ID 64</t>
+  </si>
+  <si>
+    <t>ZLPDOOK10RKB0</t>
+  </si>
+  <si>
+    <t>407731639110473</t>
+  </si>
+  <si>
+    <t>App ID 90</t>
+  </si>
+  <si>
+    <t>ZLPS4ESSN5G6V</t>
+  </si>
+  <si>
+    <t>549341994478029</t>
+  </si>
+  <si>
+    <t>App ID 41</t>
+  </si>
+  <si>
+    <t>ZLPJTMPB5EWG1</t>
+  </si>
+  <si>
+    <t>986858033673038</t>
+  </si>
+  <si>
+    <t>App ID 28</t>
+  </si>
+  <si>
+    <t>ZLPYXAHG0K8NL</t>
+  </si>
+  <si>
+    <t>603505783966854</t>
+  </si>
+  <si>
+    <t>App ID 70</t>
+  </si>
+  <si>
+    <t>ZLPKP5QE45QIV</t>
+  </si>
+  <si>
+    <t>162754619269045</t>
+  </si>
+  <si>
+    <t>App ID 53</t>
+  </si>
+  <si>
+    <t>ZLPW3H849MC99</t>
+  </si>
+  <si>
+    <t>083112733727333</t>
+  </si>
+  <si>
+    <t>App ID 48</t>
+  </si>
+  <si>
+    <t>ZLPGZDI23YB3Y</t>
+  </si>
+  <si>
+    <t>674689363431918</t>
+  </si>
+  <si>
+    <t>App ID 20</t>
+  </si>
+  <si>
+    <t>Thanh toán mua A</t>
+  </si>
+  <si>
+    <t>ZLPWR5SVTRLST</t>
+  </si>
+  <si>
+    <t>072140622304940</t>
+  </si>
+  <si>
+    <t>App ID 79</t>
+  </si>
+  <si>
+    <t>ZLPMQHVQO7JPJ</t>
+  </si>
+  <si>
+    <t>367852019309483</t>
+  </si>
+  <si>
+    <t>App ID 52</t>
+  </si>
+  <si>
+    <t>ZLPB7RT78HT7V</t>
+  </si>
+  <si>
+    <t>628393557198049</t>
+  </si>
+  <si>
+    <t>App ID 54</t>
+  </si>
+  <si>
+    <t>99942 VND</t>
+  </si>
+  <si>
+    <t>ZLPS4DXY2X7TM</t>
+  </si>
+  <si>
+    <t>139499293942199</t>
+  </si>
+  <si>
+    <t>App ID 31</t>
+  </si>
+  <si>
+    <t>32782 VND</t>
+  </si>
+  <si>
+    <t>ZLPGWU579ZZF7</t>
+  </si>
+  <si>
+    <t>836245612375809</t>
+  </si>
+  <si>
+    <t>App ID 77</t>
+  </si>
+  <si>
+    <t>88556 VND</t>
+  </si>
+  <si>
+    <t>ZLPMR6IHWWSOR</t>
+  </si>
+  <si>
+    <t>559365966284440</t>
+  </si>
+  <si>
+    <t>App ID 83</t>
+  </si>
+  <si>
+    <t>97196 VND</t>
+  </si>
+  <si>
+    <t>ZLPI2RQBRWB30</t>
+  </si>
+  <si>
+    <t>289899977421877</t>
+  </si>
+  <si>
+    <t>App ID 13</t>
+  </si>
+  <si>
+    <t>89366 VND</t>
+  </si>
+  <si>
+    <t>ZLPMLZHE0XSX7</t>
+  </si>
+  <si>
+    <t>990727091936417</t>
+  </si>
+  <si>
+    <t>App ID 84</t>
+  </si>
+  <si>
+    <t>ZLPRFA5QRMW71</t>
+  </si>
+  <si>
+    <t>140626558541448</t>
+  </si>
+  <si>
+    <t>ZLPFO2ZGISLP3</t>
+  </si>
+  <si>
+    <t>826255872263995</t>
+  </si>
+  <si>
+    <t>39012 VND</t>
+  </si>
+  <si>
+    <t>ZLP2RQH3OPUJF</t>
+  </si>
+  <si>
+    <t>040726052562121</t>
+  </si>
+  <si>
+    <t>App ID 11</t>
+  </si>
+  <si>
+    <t>62216 VND</t>
+  </si>
+  <si>
+    <t>ZLP76TRJB3P74</t>
+  </si>
+  <si>
+    <t>093681024290613</t>
+  </si>
+  <si>
+    <t>App ID 37</t>
+  </si>
+  <si>
+    <t>54812 VND</t>
+  </si>
+  <si>
+    <t>ZLPMNN214U8TF</t>
+  </si>
+  <si>
+    <t>131746893330070</t>
+  </si>
+  <si>
+    <t>22338 VND</t>
+  </si>
+  <si>
+    <t>ZLPTQ5LNNNKRR</t>
+  </si>
+  <si>
+    <t>862374082100115</t>
+  </si>
+  <si>
+    <t>App ID 40</t>
+  </si>
+  <si>
+    <t>92114 VND</t>
+  </si>
+  <si>
+    <t>ZLP9I3V4OQF8R</t>
+  </si>
+  <si>
+    <t>088422840406908</t>
+  </si>
+  <si>
+    <t>App ID 32</t>
+  </si>
+  <si>
+    <t>23098 VND</t>
+  </si>
+  <si>
+    <t>ZLPB0GL712GFH</t>
+  </si>
+  <si>
+    <t>966368144121728</t>
+  </si>
+  <si>
+    <t>App ID 69</t>
+  </si>
+  <si>
+    <t>36508 VND</t>
+  </si>
+  <si>
+    <t>ZLPY1I3HSVE7Q</t>
+  </si>
+  <si>
+    <t>042005018641734</t>
+  </si>
+  <si>
+    <t>App ID 60</t>
+  </si>
+  <si>
+    <t>85983 VND</t>
+  </si>
+  <si>
+    <t>ZLPO5SSPMU2X9</t>
+  </si>
+  <si>
+    <t>787836293461537</t>
+  </si>
+  <si>
+    <t>App ID 80</t>
+  </si>
+  <si>
+    <t>47456 VND</t>
+  </si>
+  <si>
+    <t>ZLP8ZDMOSG5WX</t>
+  </si>
+  <si>
+    <t>597980122270621</t>
+  </si>
+  <si>
+    <t>86114 VND</t>
+  </si>
+  <si>
+    <t>ZLP6GIS8BF3EB</t>
+  </si>
+  <si>
+    <t>785354275373669</t>
+  </si>
+  <si>
+    <t>App ID 76</t>
+  </si>
+  <si>
+    <t>34588 VND</t>
+  </si>
+  <si>
+    <t>ZLPFTXQBZEI49</t>
+  </si>
+  <si>
+    <t>469830243967144</t>
+  </si>
+  <si>
+    <t>App ID 29</t>
+  </si>
+  <si>
+    <t>98626 VND</t>
+  </si>
+  <si>
+    <t>ZLPNSXG8BVQQN</t>
+  </si>
+  <si>
+    <t>149081712386131</t>
+  </si>
+  <si>
+    <t>App ID 55</t>
+  </si>
+  <si>
+    <t>65802 VND</t>
+  </si>
+  <si>
+    <t>ZLPVKBGW8VLTG</t>
+  </si>
+  <si>
+    <t>121306945876347</t>
+  </si>
+  <si>
+    <t>App ID 43</t>
+  </si>
+  <si>
+    <t>52375 VND</t>
+  </si>
+  <si>
+    <t>ZLPCIT3F0VRBU</t>
+  </si>
+  <si>
+    <t>935819320316980</t>
+  </si>
+  <si>
+    <t>87724 VND</t>
+  </si>
+  <si>
+    <t>ZLPPEC6UPMI10</t>
+  </si>
+  <si>
+    <t>920436788657282</t>
+  </si>
+  <si>
+    <t>App ID 5</t>
+  </si>
+  <si>
+    <t>ZLPDFW5PCSZ7I</t>
+  </si>
+  <si>
+    <t>139880535197230</t>
+  </si>
+  <si>
+    <t>App ID 21</t>
+  </si>
+  <si>
+    <t>ZLP3M7W445IUX</t>
+  </si>
+  <si>
+    <t>712448689173744</t>
+  </si>
+  <si>
+    <t>App ID 50</t>
+  </si>
+  <si>
+    <t>ZLPNKBBYYDY7U</t>
+  </si>
+  <si>
+    <t>468270856570721</t>
+  </si>
+  <si>
+    <t>ZLP314EI8J44K</t>
+  </si>
+  <si>
+    <t>646096978085425</t>
+  </si>
+  <si>
+    <t>App ID 99</t>
+  </si>
+  <si>
+    <t>ZLPDQ0ISSGSWH</t>
+  </si>
+  <si>
+    <t>872410444589249</t>
+  </si>
+  <si>
+    <t>App ID 35</t>
+  </si>
+  <si>
+    <t>ZLPVPLHWODMWT</t>
+  </si>
+  <si>
+    <t>558458734447938</t>
+  </si>
+  <si>
+    <t>App ID 81</t>
+  </si>
+  <si>
+    <t>ZLPAPX6LET65Z</t>
+  </si>
+  <si>
+    <t>931926342906861</t>
+  </si>
+  <si>
+    <t>ZLPFT06AEJBNU</t>
+  </si>
+  <si>
+    <t>880081597792606</t>
+  </si>
+  <si>
+    <t>78957 VND</t>
+  </si>
+  <si>
+    <t>ZLPYV21G68D2G</t>
+  </si>
+  <si>
+    <t>923907265150849</t>
+  </si>
+  <si>
+    <t>App ID 34</t>
+  </si>
+  <si>
+    <t>14795 VND</t>
+  </si>
+  <si>
+    <t>ZLP9IT4OZTRH9</t>
+  </si>
+  <si>
+    <t>814566210919988</t>
+  </si>
+  <si>
+    <t>App ID 87</t>
+  </si>
+  <si>
+    <t>96887 VND</t>
+  </si>
+  <si>
+    <t>ZLP9LE7MQIKVW</t>
+  </si>
+  <si>
+    <t>812215016442052</t>
+  </si>
+  <si>
+    <t>App ID 93</t>
+  </si>
+  <si>
+    <t>69733 VND</t>
+  </si>
+  <si>
+    <t>ZLPU1SL7G9MOM</t>
+  </si>
+  <si>
+    <t>683036053714003</t>
+  </si>
+  <si>
+    <t>34083 VND</t>
+  </si>
+  <si>
+    <t>ZLPTRS7FS090F</t>
+  </si>
+  <si>
+    <t>496821988095023</t>
+  </si>
+  <si>
+    <t>App ID 71</t>
+  </si>
+  <si>
+    <t>ZLPJ8M3FCH6SW</t>
+  </si>
+  <si>
+    <t>961270595136880</t>
+  </si>
+  <si>
+    <t>App ID 10</t>
+  </si>
+  <si>
+    <t>ZLP3BMOMX3NSS</t>
+  </si>
+  <si>
+    <t>042780916184001</t>
+  </si>
+  <si>
+    <t>ZLPS8MBKEYMVV</t>
+  </si>
+  <si>
+    <t>279778791911670</t>
+  </si>
+  <si>
+    <t>App ID 2</t>
+  </si>
+  <si>
+    <t>ZLP2TF87JXY12</t>
+  </si>
+  <si>
+    <t>834767890375053</t>
+  </si>
+  <si>
+    <t>App ID 57</t>
+  </si>
+  <si>
+    <t>ZLPSTRXDPY3BH</t>
+  </si>
+  <si>
+    <t>893977903289965</t>
+  </si>
+  <si>
+    <t>App ID 30</t>
+  </si>
+  <si>
+    <t>ngay_tao_vi</t>
+  </si>
+  <si>
+    <t>ngay_lien_ket</t>
+  </si>
+  <si>
+    <t>lien_ket_lan_dau</t>
+  </si>
+  <si>
+    <t>so_du</t>
+  </si>
+  <si>
+    <t>1000000 VND</t>
+  </si>
+  <si>
+    <t>299999 VND</t>
   </si>
 </sst>
 </file>
@@ -1090,74 +1663,66 @@
         <v>10</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>17</v>
+        <v>354</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>19</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="str">
-        <f ca="1">"Bank "&amp;RANDBETWEEN(1,3)</f>
-        <v>Bank 3</v>
+      <c r="A2" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="9" t="str">
-        <f ca="1">"ZLP"&amp;_xlfn.TEXTJOIN("",TRUE,MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1))</f>
-        <v>ZLPZ4OSLCGXDL</v>
-      </c>
-      <c r="E2" s="9" t="str">
-        <f ca="1">TEXT(RANDBETWEEN(0,999999999),"000000000")&amp;TEXT(RANDBETWEEN(0,999999),"000000")</f>
-        <v>389958095566225</v>
-      </c>
-      <c r="F2" s="9" t="str">
-        <f ca="1">"App ID "&amp;RANDBETWEEN(1,100)</f>
-        <v>App ID 26</v>
+        <v>72</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I2" s="19">
         <v>199000</v>
       </c>
-      <c r="J2" s="9" t="str">
-        <f ca="1">"transtype"&amp;RANDBETWEEN(1,3)</f>
-        <v>transtype3</v>
+      <c r="J2" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N2" s="9" t="str">
-        <f>C2</f>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">"Thanh toán mua "&amp;CHOOSE(RANDBETWEEN(1,3),"A","B","C")</f>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P2" s="18" t="str">
-        <f ca="1">RANDBETWEEN(10000,99999)&amp;" VND"</f>
-        <v>19185 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q2" s="21">
         <v>45676</v>
@@ -1171,61 +1736,53 @@
       <c r="T2" s="10"/>
     </row>
     <row r="3" spans="1:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="str">
-        <f t="shared" ref="A3:A56" ca="1" si="0">"Bank "&amp;RANDBETWEEN(1,3)</f>
-        <v>Bank 1</v>
+      <c r="A3" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f t="shared" ref="D3:D56" ca="1" si="1">"ZLP"&amp;_xlfn.TEXTJOIN("",TRUE,MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1),MID("ABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789",RANDBETWEEN(1,36),1))</f>
-        <v>ZLP75H2KWWNQZ</v>
-      </c>
-      <c r="E3" s="9" t="str">
-        <f t="shared" ref="E3:E56" ca="1" si="2">TEXT(RANDBETWEEN(0,999999999),"000000000")&amp;TEXT(RANDBETWEEN(0,999999),"000000")</f>
-        <v>280745263288044</v>
-      </c>
-      <c r="F3" s="9" t="str">
-        <f t="shared" ref="F3:F56" ca="1" si="3">"App ID "&amp;RANDBETWEEN(1,100)</f>
-        <v>App ID 54</v>
+        <v>72</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>174</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I3" s="19">
         <v>199000</v>
       </c>
-      <c r="J3" s="9" t="str">
-        <f t="shared" ref="J3:J56" ca="1" si="4">"transtype"&amp;RANDBETWEEN(1,3)</f>
-        <v>transtype3</v>
+      <c r="J3" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" s="9" t="str">
-        <f t="shared" ref="N3:N56" si="5">C3</f>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O3" s="9" t="str">
-        <f t="shared" ref="O3:O56" ca="1" si="6">"Thanh toán mua "&amp;CHOOSE(RANDBETWEEN(1,3),"A","B","C")</f>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P3" s="18" t="str">
-        <f t="shared" ref="P3:P56" ca="1" si="7">RANDBETWEEN(10000,99999)&amp;" VND"</f>
-        <v>86418 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q3" s="21">
         <v>46003</v>
@@ -1239,61 +1796,53 @@
       <c r="T3" s="10"/>
     </row>
     <row r="4" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A4" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP15N6QGNJ1L</v>
-      </c>
-      <c r="E4" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>527105491294756</v>
-      </c>
-      <c r="F4" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 83</v>
+        <v>72</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I4" s="19">
         <v>199000</v>
       </c>
-      <c r="J4" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J4" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N4" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O4" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P4" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>83212 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q4" s="21">
         <v>46175</v>
@@ -1307,61 +1856,53 @@
       <c r="T4" s="4"/>
     </row>
     <row r="5" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A5" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPFR2ILXEDTX</v>
-      </c>
-      <c r="E5" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>664480848353345</v>
-      </c>
-      <c r="F5" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 7</v>
+        <v>72</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I5" s="19">
         <v>1999999</v>
       </c>
-      <c r="J5" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J5" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N5" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O5" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P5" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>83091 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q5" s="21">
         <v>46175</v>
@@ -1375,61 +1916,53 @@
       <c r="T5" s="4"/>
     </row>
     <row r="6" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A6" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP064GQ9QUR2</v>
-      </c>
-      <c r="E6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>568860822321450</v>
-      </c>
-      <c r="F6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 66</v>
+        <v>72</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I6" s="19">
         <v>500000</v>
       </c>
-      <c r="J6" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J6" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N6" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O6" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P6" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>13247 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q6" s="21">
         <v>46175</v>
@@ -1443,61 +1976,53 @@
       <c r="T6" s="4"/>
     </row>
     <row r="7" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A7" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPDMK02QOMDV</v>
-      </c>
-      <c r="E7" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>124432866093068</v>
-      </c>
-      <c r="F7" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 13</v>
+        <v>72</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I7" s="19">
         <v>1500000</v>
       </c>
-      <c r="J7" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J7" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N7" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserRJE35QG72M</v>
-      </c>
-      <c r="O7" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P7" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>85097 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q7" s="21">
         <v>46175</v>
@@ -1511,61 +2036,53 @@
       <c r="T7" s="4"/>
     </row>
     <row r="8" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A8" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPWHPG00VU8M</v>
-      </c>
-      <c r="E8" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>064001879749375</v>
-      </c>
-      <c r="F8" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 72</v>
+        <v>73</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I8" s="19">
         <v>1500000</v>
       </c>
-      <c r="J8" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J8" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N8" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O8" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P8" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>72161 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q8" s="21">
         <v>46175</v>
@@ -1579,61 +2096,53 @@
       <c r="T8" s="4"/>
     </row>
     <row r="9" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A9" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPHTBVOPNLJ0</v>
-      </c>
-      <c r="E9" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>956036669608409</v>
-      </c>
-      <c r="F9" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 55</v>
+        <v>73</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I9" s="19">
         <v>1500000</v>
       </c>
-      <c r="J9" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J9" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N9" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O9" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P9" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>74803 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q9" s="21">
         <v>46160</v>
@@ -1647,61 +2156,53 @@
       <c r="T9" s="4"/>
     </row>
     <row r="10" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A10" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPB0S5P9ZL33</v>
-      </c>
-      <c r="E10" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>417418451992566</v>
-      </c>
-      <c r="F10" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 52</v>
+        <v>73</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I10" s="19">
         <v>1500000</v>
       </c>
-      <c r="J10" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J10" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N10" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O10" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P10" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>75880 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q10" s="21">
         <v>46160</v>
@@ -1715,61 +2216,53 @@
       <c r="T10" s="4"/>
     </row>
     <row r="11" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A11" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPTGEEHJGPVV</v>
-      </c>
-      <c r="E11" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>250492409182846</v>
-      </c>
-      <c r="F11" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 31</v>
+        <v>73</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>202</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I11" s="19">
         <v>500000</v>
       </c>
-      <c r="J11" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J11" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N11" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O11" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P11" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>77449 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q11" s="21">
         <v>46160</v>
@@ -1783,61 +2276,53 @@
       <c r="T11" s="4"/>
     </row>
     <row r="12" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A12" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPA3O8AGRGF7</v>
-      </c>
-      <c r="E12" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>085421023163655</v>
-      </c>
-      <c r="F12" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 83</v>
+        <v>73</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I12" s="19">
         <v>1500000</v>
       </c>
-      <c r="J12" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J12" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N12" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O12" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P12" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>91492 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q12" s="21">
         <v>46160</v>
@@ -1851,61 +2336,53 @@
       <c r="T12" s="4"/>
     </row>
     <row r="13" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A13" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPOUSHYPY54H</v>
-      </c>
-      <c r="E13" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>676973976151934</v>
-      </c>
-      <c r="F13" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 57</v>
+        <v>73</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I13" s="19">
         <v>1500000</v>
       </c>
-      <c r="J13" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J13" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N13" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O13" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P13" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>45633 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q13" s="21">
         <v>46160</v>
@@ -1919,61 +2396,53 @@
       <c r="T13" s="4"/>
     </row>
     <row r="14" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A14" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPTZ6TFC14E1</v>
-      </c>
-      <c r="E14" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>624392828805518</v>
-      </c>
-      <c r="F14" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 49</v>
+        <v>73</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I14" s="19">
         <v>500000</v>
       </c>
-      <c r="J14" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J14" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N14" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O14" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P14" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>75685 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q14" s="21">
         <v>46160</v>
@@ -1987,61 +2456,53 @@
       <c r="T14" s="4"/>
     </row>
     <row r="15" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A15" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPRJVBS37H3O</v>
-      </c>
-      <c r="E15" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>593302125634596</v>
-      </c>
-      <c r="F15" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 27</v>
+        <v>73</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I15" s="19">
         <v>1500000</v>
       </c>
-      <c r="J15" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J15" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N15" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserTX8PGNQFOD</v>
-      </c>
-      <c r="O15" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P15" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>97875 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="Q15" s="21">
         <v>46160</v>
@@ -2055,61 +2516,53 @@
       <c r="T15" s="4"/>
     </row>
     <row r="16" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A16" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPPEE8MP4UT1</v>
-      </c>
-      <c r="E16" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>127058360917388</v>
-      </c>
-      <c r="F16" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 95</v>
+        <v>74</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I16" s="19">
         <v>1500000</v>
       </c>
-      <c r="J16" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J16" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N16" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserKW4WN5O0B5</v>
-      </c>
-      <c r="O16" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P16" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>56750 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>219</v>
       </c>
       <c r="Q16" s="21">
         <v>43204</v>
@@ -2123,61 +2576,53 @@
       <c r="T16" s="4"/>
     </row>
     <row r="17" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A17" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPIE2OSONUHL</v>
-      </c>
-      <c r="E17" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>198970989330191</v>
-      </c>
-      <c r="F17" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 83</v>
+        <v>75</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I17" s="19">
         <v>1500000</v>
       </c>
-      <c r="J17" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J17" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N17" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>User63DNGCE75B</v>
-      </c>
-      <c r="O17" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P17" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>35002 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>223</v>
       </c>
       <c r="Q17" s="21">
         <v>43204</v>
@@ -2191,61 +2636,53 @@
       <c r="T17" s="4"/>
     </row>
     <row r="18" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A18" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPFIH7ZS9W3V</v>
-      </c>
-      <c r="E18" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>573384309720440</v>
-      </c>
-      <c r="F18" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 42</v>
+        <v>76</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I18" s="19">
         <v>2000000</v>
       </c>
-      <c r="J18" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J18" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N18" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserHXDRGBBJHU</v>
-      </c>
-      <c r="O18" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P18" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>83335 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>227</v>
       </c>
       <c r="Q18" s="21">
         <v>43204</v>
@@ -2259,61 +2696,53 @@
       <c r="T18" s="4"/>
     </row>
     <row r="19" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A19" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP3CW6A2VQEB</v>
-      </c>
-      <c r="E19" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>386231857364490</v>
-      </c>
-      <c r="F19" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 74</v>
+        <v>77</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I19" s="19">
         <v>2000000</v>
       </c>
-      <c r="J19" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J19" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N19" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserLFJCZPEWF9</v>
-      </c>
-      <c r="O19" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P19" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>12454 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>231</v>
       </c>
       <c r="Q19" s="21">
         <v>45973</v>
@@ -2327,61 +2756,53 @@
       <c r="T19" s="4"/>
     </row>
     <row r="20" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A20" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPEVN551HOGL</v>
-      </c>
-      <c r="E20" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>847761776995100</v>
-      </c>
-      <c r="F20" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 85</v>
+        <v>78</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>234</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I20" s="19">
         <v>29000</v>
       </c>
-      <c r="J20" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J20" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N20" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserAEQ59UAXQ5</v>
-      </c>
-      <c r="O20" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P20" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>15597 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="Q20" s="21">
         <v>43856</v>
@@ -2395,61 +2816,53 @@
       <c r="T20" s="4"/>
     </row>
     <row r="21" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A21" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP6CXAKQXE7A</v>
-      </c>
-      <c r="E21" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>687757239375945</v>
-      </c>
-      <c r="F21" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 80</v>
+        <v>78</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I21" s="19">
         <v>519000</v>
       </c>
-      <c r="J21" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J21" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N21" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserAEQ59UAXQ5</v>
-      </c>
-      <c r="O21" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P21" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>76126 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="Q21" s="21">
         <v>43856</v>
@@ -2463,61 +2876,53 @@
       <c r="T21" s="4"/>
     </row>
     <row r="22" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A22" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPAVJ6NB0EF7</v>
-      </c>
-      <c r="E22" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>687183533588196</v>
-      </c>
-      <c r="F22" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 6</v>
+        <v>78</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I22" s="19">
         <v>1999999</v>
       </c>
-      <c r="J22" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J22" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N22" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserAEQ59UAXQ5</v>
-      </c>
-      <c r="O22" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P22" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>47784 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="Q22" s="21">
         <v>43856</v>
@@ -2531,61 +2936,53 @@
       <c r="T22" s="4"/>
     </row>
     <row r="23" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A23" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP3UEJSDQHK6</v>
-      </c>
-      <c r="E23" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>421658810528688</v>
-      </c>
-      <c r="F23" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 65</v>
+        <v>79</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I23" s="19">
         <v>1999999</v>
       </c>
-      <c r="J23" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J23" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N23" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserA8Y80IFOVC</v>
-      </c>
-      <c r="O23" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P23" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>60877 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="Q23" s="21">
         <v>45676</v>
@@ -2599,61 +2996,53 @@
       <c r="T23" s="4"/>
     </row>
     <row r="24" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A24" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPTR63XM8ST1</v>
-      </c>
-      <c r="E24" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>809136301434572</v>
-      </c>
-      <c r="F24" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 17</v>
+        <v>80</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I24" s="19">
         <v>1999999</v>
       </c>
-      <c r="J24" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J24" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N24" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserDKWZ600G4K</v>
-      </c>
-      <c r="O24" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P24" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>60089 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>247</v>
       </c>
       <c r="Q24" s="21">
         <v>46003</v>
@@ -2667,61 +3056,53 @@
       <c r="T24" s="4"/>
     </row>
     <row r="25" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A25" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP4J921A7I5Q</v>
-      </c>
-      <c r="E25" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>147322477022342</v>
-      </c>
-      <c r="F25" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 32</v>
+        <v>81</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I25" s="19">
         <v>1000000</v>
       </c>
-      <c r="J25" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J25" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N25" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserOTC6G7HQLG</v>
-      </c>
-      <c r="O25" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P25" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>38432 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>251</v>
       </c>
       <c r="Q25" s="21">
         <v>46175</v>
@@ -2735,61 +3116,53 @@
       <c r="T25" s="4"/>
     </row>
     <row r="26" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A26" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP6RWZO0Y439</v>
-      </c>
-      <c r="E26" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>000705357630904</v>
-      </c>
-      <c r="F26" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 90</v>
+        <v>82</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I26" s="19">
         <v>1940000</v>
       </c>
-      <c r="J26" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J26" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N26" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserLH2YQQNHZO</v>
-      </c>
-      <c r="O26" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P26" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>17643 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>254</v>
       </c>
       <c r="Q26" s="21">
         <v>46175</v>
@@ -2803,61 +3176,53 @@
       <c r="T26" s="4"/>
     </row>
     <row r="27" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A27" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPFQO2PLANWE</v>
-      </c>
-      <c r="E27" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>683272534750695</v>
-      </c>
-      <c r="F27" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 60</v>
+        <v>83</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I27" s="19">
         <v>969000</v>
       </c>
-      <c r="J27" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J27" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N27" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserICTR6GF5M1</v>
-      </c>
-      <c r="O27" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P27" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>25874 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>258</v>
       </c>
       <c r="Q27" s="21">
         <v>46175</v>
@@ -2871,61 +3236,53 @@
       <c r="T27" s="4"/>
     </row>
     <row r="28" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A28" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPOUT1UPINSG</v>
-      </c>
-      <c r="E28" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>526732723024725</v>
-      </c>
-      <c r="F28" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 94</v>
+        <v>84</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I28" s="19">
         <v>3417000</v>
       </c>
-      <c r="J28" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J28" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N28" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserQKAQLCPR6W</v>
-      </c>
-      <c r="O28" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P28" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>64793 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>262</v>
       </c>
       <c r="Q28" s="21">
         <v>46175</v>
@@ -2939,61 +3296,53 @@
       <c r="T28" s="4"/>
     </row>
     <row r="29" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A29" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPEI8FPIJA5K</v>
-      </c>
-      <c r="E29" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>394380857753400</v>
-      </c>
-      <c r="F29" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 46</v>
+        <v>85</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I29" s="19">
         <v>3000000</v>
       </c>
-      <c r="J29" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J29" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N29" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserLFP6M7ZO9N</v>
-      </c>
-      <c r="O29" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P29" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>24082 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>266</v>
       </c>
       <c r="Q29" s="21">
         <v>46175</v>
@@ -3007,61 +3356,53 @@
       <c r="T29" s="4"/>
     </row>
     <row r="30" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A30" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP4JZZPP2S37</v>
-      </c>
-      <c r="E30" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>587033787026184</v>
-      </c>
-      <c r="F30" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 1</v>
+        <v>86</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I30" s="19">
         <v>3624997</v>
       </c>
-      <c r="J30" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J30" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N30" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>User7GPN2OGLCL</v>
-      </c>
-      <c r="O30" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P30" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>15927 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="Q30" s="21">
         <v>46160</v>
@@ -3075,61 +3416,53 @@
       <c r="T30" s="4"/>
     </row>
     <row r="31" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A31" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPG73RIMSH2P</v>
-      </c>
-      <c r="E31" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>516968184083328</v>
-      </c>
-      <c r="F31" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 23</v>
+        <v>87</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I31" s="19">
         <v>426650</v>
       </c>
-      <c r="J31" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J31" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N31" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserPZXBRS4RTH</v>
-      </c>
-      <c r="O31" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P31" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>33695 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>274</v>
       </c>
       <c r="Q31" s="21">
         <v>46160</v>
@@ -3143,61 +3476,53 @@
       <c r="T31" s="4"/>
     </row>
     <row r="32" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A32" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP5VI93KWV90</v>
-      </c>
-      <c r="E32" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>657428844088075</v>
-      </c>
-      <c r="F32" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 41</v>
+        <v>88</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I32" s="19">
         <v>5000000</v>
       </c>
-      <c r="J32" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J32" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N32" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserNJAZGBPLX7</v>
-      </c>
-      <c r="O32" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P32" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>69986 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>277</v>
       </c>
       <c r="Q32" s="21">
         <v>46160</v>
@@ -3211,61 +3536,53 @@
       <c r="T32" s="4"/>
     </row>
     <row r="33" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A33" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPM35NMQV91V</v>
-      </c>
-      <c r="E33" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>912310823455759</v>
-      </c>
-      <c r="F33" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 83</v>
+        <v>89</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>280</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I33" s="19">
         <v>2000000</v>
       </c>
-      <c r="J33" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J33" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N33" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserHCWN1VQTZF</v>
-      </c>
-      <c r="O33" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P33" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>72770 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>281</v>
       </c>
       <c r="Q33" s="21">
         <v>46160</v>
@@ -3279,61 +3596,53 @@
       <c r="T33" s="4"/>
     </row>
     <row r="34" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A34" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPWL3VZFT4V5</v>
-      </c>
-      <c r="E34" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>771380498999469</v>
-      </c>
-      <c r="F34" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 87</v>
+        <v>90</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>284</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I34" s="19">
         <v>500000</v>
       </c>
-      <c r="J34" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J34" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N34" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>User4M4F64YJPU</v>
-      </c>
-      <c r="O34" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P34" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>30529 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>285</v>
       </c>
       <c r="Q34" s="21">
         <v>46160</v>
@@ -3347,61 +3656,53 @@
       <c r="T34" s="4"/>
     </row>
     <row r="35" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A35" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPADBHFI2WGZ</v>
-      </c>
-      <c r="E35" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>025711324401972</v>
-      </c>
-      <c r="F35" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 34</v>
+        <v>91</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>288</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I35" s="19">
         <v>1000000</v>
       </c>
-      <c r="J35" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J35" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N35" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserFDS3W372JX</v>
-      </c>
-      <c r="O35" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P35" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>44222 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P35" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="Q35" s="21">
         <v>46160</v>
@@ -3415,61 +3716,53 @@
       <c r="T35" s="4"/>
     </row>
     <row r="36" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A36" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP2J4BHCTTNI</v>
-      </c>
-      <c r="E36" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>571569156956335</v>
-      </c>
-      <c r="F36" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 5</v>
+        <v>92</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>292</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I36" s="19">
         <v>970000</v>
       </c>
-      <c r="J36" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J36" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N36" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>User6AVHVEN0BO</v>
-      </c>
-      <c r="O36" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P36" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>62957 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>293</v>
       </c>
       <c r="Q36" s="21">
         <v>46160</v>
@@ -3483,61 +3776,53 @@
       <c r="T36" s="4"/>
     </row>
     <row r="37" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A37" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPA1JS6ISNPV</v>
-      </c>
-      <c r="E37" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>663944027649241</v>
-      </c>
-      <c r="F37" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 85</v>
+        <v>93</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I37" s="19">
         <v>485000</v>
       </c>
-      <c r="J37" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J37" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N37" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserBDO4JZB9SO</v>
-      </c>
-      <c r="O37" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P37" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>32340 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>296</v>
       </c>
       <c r="Q37" s="21">
         <v>43204</v>
@@ -3551,61 +3836,53 @@
       <c r="T37" s="4"/>
     </row>
     <row r="38" spans="1:20" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A38" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPRF5IVA6TRO</v>
-      </c>
-      <c r="E38" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>109362605331185</v>
-      </c>
-      <c r="F38" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 100</v>
+        <v>94</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I38" s="19">
         <v>194000</v>
       </c>
-      <c r="J38" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J38" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N38" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O38" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P38" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>68801 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q38" s="21">
         <v>43204</v>
@@ -3619,61 +3896,53 @@
       <c r="T38" s="4"/>
     </row>
     <row r="39" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A39" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPZ7PVK3PNYL</v>
-      </c>
-      <c r="E39" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>340385793034325</v>
-      </c>
-      <c r="F39" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 28</v>
+        <v>94</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I39" s="19">
         <v>199000</v>
       </c>
-      <c r="J39" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J39" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N39" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O39" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P39" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>19971 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q39" s="21">
         <v>43204</v>
@@ -3687,61 +3956,53 @@
       <c r="T39" s="4"/>
     </row>
     <row r="40" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A40" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPFQMRLI9CAP</v>
-      </c>
-      <c r="E40" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>494776571475097</v>
-      </c>
-      <c r="F40" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 7</v>
+        <v>94</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I40" s="19">
         <v>199000</v>
       </c>
-      <c r="J40" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J40" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N40" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O40" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P40" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>12128 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N40" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q40" s="21">
         <v>45973</v>
@@ -3755,61 +4016,53 @@
       <c r="T40" s="4"/>
     </row>
     <row r="41" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A41" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPLRNWKU19AD</v>
-      </c>
-      <c r="E41" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>585259189429194</v>
-      </c>
-      <c r="F41" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 31</v>
+        <v>94</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I41" s="19">
         <v>199000</v>
       </c>
-      <c r="J41" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J41" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N41" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O41" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P41" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>61938 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P41" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q41" s="21">
         <v>43856</v>
@@ -3823,61 +4076,53 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A42" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP84NFWPCU1W</v>
-      </c>
-      <c r="E42" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>113279326875077</v>
-      </c>
-      <c r="F42" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 79</v>
+        <v>94</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I42" s="19">
         <v>1999999</v>
       </c>
-      <c r="J42" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J42" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N42" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O42" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P42" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>27938 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P42" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q42" s="21">
         <v>43856</v>
@@ -3891,61 +4136,53 @@
       <c r="T42" s="4"/>
     </row>
     <row r="43" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A43" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPP4JWJVQQT0</v>
-      </c>
-      <c r="E43" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>801466410484482</v>
-      </c>
-      <c r="F43" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 48</v>
+        <v>94</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>313</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I43" s="19">
         <v>500000</v>
       </c>
-      <c r="J43" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J43" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N43" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O43" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P43" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>35826 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P43" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q43" s="21">
         <v>43856</v>
@@ -3959,61 +4196,53 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A44" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPGTHMUVUBGS</v>
-      </c>
-      <c r="E44" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>063132839790187</v>
-      </c>
-      <c r="F44" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 74</v>
+        <v>94</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>316</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I44" s="19">
         <v>1500000</v>
       </c>
-      <c r="J44" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J44" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N44" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O44" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P44" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>17141 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N44" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P44" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q44" s="21">
         <v>44994</v>
@@ -4027,61 +4256,53 @@
       <c r="T44" s="4"/>
     </row>
     <row r="45" spans="1:20" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A45" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP7CCC7X3P0K</v>
-      </c>
-      <c r="E45" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>634643902508229</v>
-      </c>
-      <c r="F45" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 1</v>
+        <v>94</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>234</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I45" s="19">
         <v>1500000</v>
       </c>
-      <c r="J45" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J45" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N45" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserE7SQMEKLDJ</v>
-      </c>
-      <c r="O45" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P45" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>22705 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P45" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="Q45" s="21">
         <v>44994</v>
@@ -4095,61 +4316,53 @@
       <c r="T45" s="4"/>
     </row>
     <row r="46" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A46" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPLF9KM0FKAU</v>
-      </c>
-      <c r="E46" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>643589927871742</v>
-      </c>
-      <c r="F46" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 68</v>
+        <v>95</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I46" s="19">
         <v>1500000</v>
       </c>
-      <c r="J46" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J46" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N46" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserI9RHIE1U67</v>
-      </c>
-      <c r="O46" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P46" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>19574 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P46" s="18" t="s">
+        <v>321</v>
       </c>
       <c r="Q46" s="21">
         <v>45931</v>
@@ -4163,61 +4376,53 @@
       <c r="T46" s="4"/>
     </row>
     <row r="47" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A47" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPQU2SMX11ZO</v>
-      </c>
-      <c r="E47" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>226425047200073</v>
-      </c>
-      <c r="F47" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 41</v>
+        <v>96</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I47" s="19">
         <v>1500000</v>
       </c>
-      <c r="J47" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J47" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N47" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserB1K29A2XRT</v>
-      </c>
-      <c r="O47" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P47" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>14828 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P47" s="18" t="s">
+        <v>325</v>
       </c>
       <c r="Q47" s="21">
         <v>45931</v>
@@ -4231,61 +4436,53 @@
       <c r="T47" s="4"/>
     </row>
     <row r="48" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A48" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPPBHLYQ7QQ6</v>
-      </c>
-      <c r="E48" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>506425932229837</v>
-      </c>
-      <c r="F48" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 13</v>
+        <v>97</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I48" s="19">
         <v>500000</v>
       </c>
-      <c r="J48" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J48" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N48" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserM7EE4WHBZ2</v>
-      </c>
-      <c r="O48" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P48" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>82072 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P48" s="18" t="s">
+        <v>329</v>
       </c>
       <c r="Q48" s="21">
         <v>45931</v>
@@ -4299,61 +4496,53 @@
       <c r="T48" s="4"/>
     </row>
     <row r="49" spans="1:19" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A49" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPWU6AWJFTZ2</v>
-      </c>
-      <c r="E49" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>174684330846334</v>
-      </c>
-      <c r="F49" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 61</v>
+        <v>98</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>332</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I49" s="19">
         <v>1500000</v>
       </c>
-      <c r="J49" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J49" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N49" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>User2I93PFXB9S</v>
-      </c>
-      <c r="O49" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P49" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>28429 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P49" s="18" t="s">
+        <v>333</v>
       </c>
       <c r="Q49" s="21">
         <v>45931</v>
@@ -4366,61 +4555,53 @@
       </c>
     </row>
     <row r="50" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A50" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP32UNEOKGJO</v>
-      </c>
-      <c r="E50" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>733926355937096</v>
-      </c>
-      <c r="F50" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 35</v>
+        <v>99</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>332</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I50" s="19">
         <v>1500000</v>
       </c>
-      <c r="J50" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J50" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N50" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O50" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P50" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>67747 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q50" s="21">
         <v>45931</v>
@@ -4433,61 +4614,53 @@
       </c>
     </row>
     <row r="51" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A51" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPVSZMN4PP13</v>
-      </c>
-      <c r="E51" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>193647369000592</v>
-      </c>
-      <c r="F51" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 59</v>
+        <v>99</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>339</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I51" s="19">
         <v>500000</v>
       </c>
-      <c r="J51" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype3</v>
+      <c r="J51" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N51" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O51" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P51" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>24567 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P51" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q51" s="21">
         <v>45378</v>
@@ -4500,61 +4673,53 @@
       </c>
     </row>
     <row r="52" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A52" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPCO09R4IOS8</v>
-      </c>
-      <c r="E52" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>124965908289071</v>
-      </c>
-      <c r="F52" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 71</v>
+        <v>99</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I52" s="19">
         <v>1500000</v>
       </c>
-      <c r="J52" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J52" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N52" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O52" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua B</v>
-      </c>
-      <c r="P52" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>27281 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P52" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q52" s="21">
         <v>45378</v>
@@ -4567,61 +4732,53 @@
       </c>
     </row>
     <row r="53" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 1</v>
+      <c r="A53" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP22MGIXVHAQ</v>
-      </c>
-      <c r="E53" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>140864479674509</v>
-      </c>
-      <c r="F53" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 77</v>
+        <v>99</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I53" s="19">
         <v>1500000</v>
       </c>
-      <c r="J53" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J53" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N53" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O53" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P53" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>74792 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q53" s="21">
         <v>45378</v>
@@ -4634,61 +4791,53 @@
       </c>
     </row>
     <row r="54" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 3</v>
+      <c r="A54" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPRYAWNZDMYD</v>
-      </c>
-      <c r="E54" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>417907556634510</v>
-      </c>
-      <c r="F54" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 35</v>
+        <v>99</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>347</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I54" s="19">
         <v>1500000</v>
       </c>
-      <c r="J54" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype2</v>
+      <c r="J54" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N54" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O54" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua C</v>
-      </c>
-      <c r="P54" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>86181 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N54" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O54" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P54" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q54" s="21">
         <v>45378</v>
@@ -4701,61 +4850,53 @@
       </c>
     </row>
     <row r="55" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A55" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D55" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLP9VAP5HP586</v>
-      </c>
-      <c r="E55" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>233547473655538</v>
-      </c>
-      <c r="F55" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 23</v>
+        <v>99</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>350</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I55" s="19">
         <v>2000000</v>
       </c>
-      <c r="J55" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J55" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N55" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O55" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P55" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>41840 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q55" s="21">
         <v>45378</v>
@@ -4768,61 +4909,53 @@
       </c>
     </row>
     <row r="56" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Bank 2</v>
+      <c r="A56" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ZLPDDHYLCI2RG</v>
-      </c>
-      <c r="E56" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>253263723479210</v>
-      </c>
-      <c r="F56" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>App ID 47</v>
+        <v>99</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>353</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I56" s="19">
         <v>2000000</v>
       </c>
-      <c r="J56" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>transtype1</v>
+      <c r="J56" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="N56" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>UserWXZWTO51JG</v>
-      </c>
-      <c r="O56" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>Thanh toán mua A</v>
-      </c>
-      <c r="P56" s="18" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>84925 VND</v>
+        <v>163</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="O56" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P56" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="Q56" s="21">
         <v>45378</v>
